--- a/QuantStudio/Resource/BaoStockDBInfo.xlsx
+++ b/QuantStudio/Resource/BaoStockDBInfo.xlsx
@@ -1,20 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="TableInfo" sheetId="3" r:id="rId1"/>
-    <sheet name="FactorInfo" sheetId="4" r:id="rId2"/>
-    <sheet name="ArgInfo" sheetId="5" r:id="rId3"/>
+    <sheet name="TableInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="FactorInfo" sheetId="2" r:id="rId2"/>
+    <sheet name="ArgInfo" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TableInfo!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FactorInfo!$A$1:$F$19</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="460">
   <si>
     <t>TableName</t>
   </si>
@@ -86,6 +82,276 @@
     <t>http://baostock.com/mainContent?file=stockIndustry.md</t>
   </si>
   <si>
+    <t>季度盈利能力</t>
+  </si>
+  <si>
+    <t>query_profit_data</t>
+  </si>
+  <si>
+    <t>QuarterTable</t>
+  </si>
+  <si>
+    <t>季频盈利能力指标</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=seasonProfit.md</t>
+  </si>
+  <si>
+    <t>除权除息信息</t>
+  </si>
+  <si>
+    <t>query_dividend_data</t>
+  </si>
+  <si>
+    <t>YearTable</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=dividInfo.md</t>
+  </si>
+  <si>
+    <t>季度营运能力</t>
+  </si>
+  <si>
+    <t>query_operation_data</t>
+  </si>
+  <si>
+    <t>季频营运能力指标</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=seasonOperate.md</t>
+  </si>
+  <si>
+    <t>季度成长能力</t>
+  </si>
+  <si>
+    <t>query_growth_data</t>
+  </si>
+  <si>
+    <t>季频成长能力指标</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=seasonGrowth.md</t>
+  </si>
+  <si>
+    <t>季度偿债能力</t>
+  </si>
+  <si>
+    <t>query_balance_data</t>
+  </si>
+  <si>
+    <t>季频偿债能力指标</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=seasonBalance.md</t>
+  </si>
+  <si>
+    <t>季度现金流量</t>
+  </si>
+  <si>
+    <t>query_cash_flow_data</t>
+  </si>
+  <si>
+    <t>季频现金流量指标</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=seasonCashFlow.md</t>
+  </si>
+  <si>
+    <t>季度杜邦指数</t>
+  </si>
+  <si>
+    <t>query_dupont_data</t>
+  </si>
+  <si>
+    <t>季频杜邦指数指标</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=seasonDuPont.md</t>
+  </si>
+  <si>
+    <t>季度业绩快报</t>
+  </si>
+  <si>
+    <t>query_performance_express_report</t>
+  </si>
+  <si>
+    <t>季频业绩快报</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=performanceExpressReport.md</t>
+  </si>
+  <si>
+    <t>季度业绩预告</t>
+  </si>
+  <si>
+    <t>query_forecast_report</t>
+  </si>
+  <si>
+    <t>季频业绩预告</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=forecastReport.md</t>
+  </si>
+  <si>
+    <t>证券基本资料</t>
+  </si>
+  <si>
+    <t>query_stock_basic</t>
+  </si>
+  <si>
+    <t>StockBasicTable</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=stockBasic.md</t>
+  </si>
+  <si>
+    <t>存款利率</t>
+  </si>
+  <si>
+    <t>query_deposit_rate_data</t>
+  </si>
+  <si>
+    <t>MacroDataTable</t>
+  </si>
+  <si>
+    <t>{"IDAdj":"无","DTFmt":"%Y-%m-%d"}</t>
+  </si>
+  <si>
+    <t>宏观</t>
+  </si>
+  <si>
+    <t>http://baostock.com/mainContent?file=depositRate.md</t>
+  </si>
+  <si>
+    <t>存款准备金率</t>
+  </si>
+  <si>
+    <t>query_required_reserve_ratio_data</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=reserveRatio.md</t>
+  </si>
+  <si>
+    <t>贷款利率</t>
+  </si>
+  <si>
+    <t>query_loan_rate_data</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=loanRate.md</t>
+  </si>
+  <si>
+    <t>货币供应量</t>
+  </si>
+  <si>
+    <t>query_money_supply_data_month</t>
+  </si>
+  <si>
+    <t>{"IDAdj":"无","DTFmt":"%Y-%m","DateAlign":"月底"}</t>
+  </si>
+  <si>
+    <t>货币供应量(月频)</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=supplyData.md</t>
+  </si>
+  <si>
+    <t>货币供应量(年底余额)</t>
+  </si>
+  <si>
+    <t>query_money_supply_data_year</t>
+  </si>
+  <si>
+    <t>{"IDAdj":"无","DTFmt":"%Y","DateAlign":"年底"}</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=supplyDataYear.md</t>
+  </si>
+  <si>
+    <t>每日A股K线</t>
+  </si>
+  <si>
+    <t>query_daily_history_k_AStock</t>
+  </si>
+  <si>
+    <t>某日所有A股日K线数据</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=DailyUpdates.md</t>
+  </si>
+  <si>
+    <t>每日ETF K线</t>
+  </si>
+  <si>
+    <t>query_daily_history_k_ETF</t>
+  </si>
+  <si>
+    <t>ETF</t>
+  </si>
+  <si>
+    <t>某日所有ETF日K线数据</t>
+  </si>
+  <si>
+    <t>每日复权因子</t>
+  </si>
+  <si>
+    <t>query_daily_adjust_factor</t>
+  </si>
+  <si>
+    <t>某日复权因子信息</t>
+  </si>
+  <si>
+    <t>每日全部A股</t>
+  </si>
+  <si>
+    <t>query_all_stock</t>
+  </si>
+  <si>
+    <t>某日所有证券基本信息</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=StockBasicInfoAPI.md</t>
+  </si>
+  <si>
+    <t>上证50成分股</t>
+  </si>
+  <si>
+    <t>query_sz50_stocks</t>
+  </si>
+  <si>
+    <t>指数</t>
+  </si>
+  <si>
+    <t>上证50成分股信息</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=sz50Stock.md</t>
+  </si>
+  <si>
+    <t>沪深300成分股</t>
+  </si>
+  <si>
+    <t>query_hs300_stocks</t>
+  </si>
+  <si>
+    <t>沪深300成分股信息</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=hs300Stock.md</t>
+  </si>
+  <si>
+    <t>中证500成分股</t>
+  </si>
+  <si>
+    <t>query_zz500_stocks</t>
+  </si>
+  <si>
+    <t>中证500成分股信息</t>
+  </si>
+  <si>
+    <t>https://baostock.com/mainContent?file=zz500Stock.md</t>
+  </si>
+  <si>
     <t>FieldName</t>
   </si>
   <si>
@@ -248,6 +514,741 @@
     <t>所属行业类别</t>
   </si>
   <si>
+    <t>股票代码</t>
+  </si>
+  <si>
+    <t>pubDate</t>
+  </si>
+  <si>
+    <t>公告日期</t>
+  </si>
+  <si>
+    <t>statDate</t>
+  </si>
+  <si>
+    <t>统计截止日期</t>
+  </si>
+  <si>
+    <t>roeAvg</t>
+  </si>
+  <si>
+    <t>净资产收益率(平均)(%)</t>
+  </si>
+  <si>
+    <t>npMargin</t>
+  </si>
+  <si>
+    <t>销售净利率(%)</t>
+  </si>
+  <si>
+    <t>gpMargin</t>
+  </si>
+  <si>
+    <t>销售毛利率(%)</t>
+  </si>
+  <si>
+    <t>netProfit</t>
+  </si>
+  <si>
+    <t>净利润(元)</t>
+  </si>
+  <si>
+    <t>epsTTM</t>
+  </si>
+  <si>
+    <t>每股收益</t>
+  </si>
+  <si>
+    <t>MBRevenue</t>
+  </si>
+  <si>
+    <t>主营营业收入(元)</t>
+  </si>
+  <si>
+    <t>totalShare</t>
+  </si>
+  <si>
+    <t>总股本</t>
+  </si>
+  <si>
+    <t>liqaShare</t>
+  </si>
+  <si>
+    <t>流通股本</t>
+  </si>
+  <si>
+    <t>dividPreNoticeDate</t>
+  </si>
+  <si>
+    <t>预批露公告日</t>
+  </si>
+  <si>
+    <t>dividAgmPumDate</t>
+  </si>
+  <si>
+    <t>股东大会公告日期</t>
+  </si>
+  <si>
+    <t>dividPlanAnnounceDate</t>
+  </si>
+  <si>
+    <t>预案公告日</t>
+  </si>
+  <si>
+    <t>dividPlanDate</t>
+  </si>
+  <si>
+    <t>分红实施公告日</t>
+  </si>
+  <si>
+    <t>dividRegistDate</t>
+  </si>
+  <si>
+    <t>股权登记告日</t>
+  </si>
+  <si>
+    <t>dividOperateDate</t>
+  </si>
+  <si>
+    <t>除权除息日期</t>
+  </si>
+  <si>
+    <t>dividPayDate</t>
+  </si>
+  <si>
+    <t>派息日</t>
+  </si>
+  <si>
+    <t>dividStockMarketDate</t>
+  </si>
+  <si>
+    <t>红股上市交易日</t>
+  </si>
+  <si>
+    <t>dividCashPsBeforeTax</t>
+  </si>
+  <si>
+    <t>每股股利(税前), 算法: 派息比例分子(税前)/派息比例分母</t>
+  </si>
+  <si>
+    <t>dividCashPsAfterTax</t>
+  </si>
+  <si>
+    <t>每股股利(税后), 算法: 派息比例分子(税后)/派息比例分母</t>
+  </si>
+  <si>
+    <t>dividStocksPs</t>
+  </si>
+  <si>
+    <t>每股红股</t>
+  </si>
+  <si>
+    <t>dividCashStock</t>
+  </si>
+  <si>
+    <t>分红送转, 算法: 每股派息数(税前)+每股送股数+每股转增股本数</t>
+  </si>
+  <si>
+    <t>dividReserveToStockPs</t>
+  </si>
+  <si>
+    <t>每股转增资本</t>
+  </si>
+  <si>
+    <t>NRTurnRatio</t>
+  </si>
+  <si>
+    <t>应收账款周转率(次), 算法: 营业收入/[(期初应收票据及应收账款净额+期末应收票据及应收账款净额)/2]</t>
+  </si>
+  <si>
+    <t>NRTurnDays</t>
+  </si>
+  <si>
+    <t>应收账款周转天数(天), 算法: 季报天数/应收账款周转率(一季报：90天，中报：180天，三季报：270天，年报：360天)</t>
+  </si>
+  <si>
+    <t>INVTurnRatio</t>
+  </si>
+  <si>
+    <t>存货周转率(次), 算法: 营业成本/[(期初存货净额+期末存货净额)/2]</t>
+  </si>
+  <si>
+    <t>INVTurnDays</t>
+  </si>
+  <si>
+    <t>存货周转天数(天), 算法: 季报天数/存货周转率(一季报：90天，中报：180天，三季报：270天，年报：360天)</t>
+  </si>
+  <si>
+    <t>CATurnRatio</t>
+  </si>
+  <si>
+    <t>流动资产周转率(次), 算法: 营业总收入/[(期初流动资产+期末流动资产)/2]</t>
+  </si>
+  <si>
+    <t>AssetTurnRatio</t>
+  </si>
+  <si>
+    <t>总资产周转率, 算法: 营业总收入/[(期初资产总额+期末资产总额)/2]</t>
+  </si>
+  <si>
+    <t>公司发布财报的日期</t>
+  </si>
+  <si>
+    <t>财报统计的季度的最后一天, 比如2017-03-31, 2017-06-30</t>
+  </si>
+  <si>
+    <t>YOYEquity</t>
+  </si>
+  <si>
+    <t>净资产同比增长率, 算法: (本期净资产-上年同期净资产)/上年同期净资产的绝对值*100%</t>
+  </si>
+  <si>
+    <t>YOYAsset</t>
+  </si>
+  <si>
+    <t>总资产同比增长率, 算法: (本期总资产-上年同期总资产)/上年同期总资产的绝对值*100%</t>
+  </si>
+  <si>
+    <t>YOYNI</t>
+  </si>
+  <si>
+    <t>净利润同比增长率, 算法: (本期净利润-上年同期净利润)/上年同期净利润的绝对值*100%</t>
+  </si>
+  <si>
+    <t>YOYEPSBasic</t>
+  </si>
+  <si>
+    <t>基本每股收益同比增长率, 算法: (本期基本每股收益-上年同期基本每股收益)/上年同期基本每股收益的绝对值*100%</t>
+  </si>
+  <si>
+    <t>YOYPNI</t>
+  </si>
+  <si>
+    <t>归属母公司股东净利润同比增长率, 算法: (本期归属母公司股东净利润-上年同期归属母公司股东净利润)/上年同期归属母公司股东净利润的绝对值*100%</t>
+  </si>
+  <si>
+    <t>财报统计的季度的最后一天</t>
+  </si>
+  <si>
+    <t>currentRatio</t>
+  </si>
+  <si>
+    <t>流动比率, 算法: 流动资产/流动负债</t>
+  </si>
+  <si>
+    <t>quickRatio</t>
+  </si>
+  <si>
+    <t>速动比率, 算法: (流动资产-存货净额)/流动负债</t>
+  </si>
+  <si>
+    <t>cashRatio</t>
+  </si>
+  <si>
+    <t>现金比率, 算法: (货币资金+交易性金融资产)/流动负债</t>
+  </si>
+  <si>
+    <t>YOYLiability</t>
+  </si>
+  <si>
+    <t>总负债同比增长率, 算法: (本期总负债-上年同期总负债)/上年同期中负债的绝对值*100%</t>
+  </si>
+  <si>
+    <t>liabilityToAsset</t>
+  </si>
+  <si>
+    <t>资产负债率, 算法: 负债总额/资产总额</t>
+  </si>
+  <si>
+    <t>assetToEquity</t>
+  </si>
+  <si>
+    <t>权益乘数, 算法: 资产总额/股东权益总额=1/(1-资产负债率)</t>
+  </si>
+  <si>
+    <t>CAToAsset</t>
+  </si>
+  <si>
+    <t>流动资产除以总资产</t>
+  </si>
+  <si>
+    <t>NCAToAsset</t>
+  </si>
+  <si>
+    <t>非流动资产除以总资产</t>
+  </si>
+  <si>
+    <t>tangibleAssetToAsset</t>
+  </si>
+  <si>
+    <t>有形资产除以总资产</t>
+  </si>
+  <si>
+    <t>ebitToInterest</t>
+  </si>
+  <si>
+    <t>已获利息倍数, 算法: 息税前利润/利息费用</t>
+  </si>
+  <si>
+    <t>CFOToOR</t>
+  </si>
+  <si>
+    <t>经营活动产生的现金流量净额除以营业收入</t>
+  </si>
+  <si>
+    <t>CFOToNP</t>
+  </si>
+  <si>
+    <t>经营性现金净流量除以净利润</t>
+  </si>
+  <si>
+    <t>CFOToGr</t>
+  </si>
+  <si>
+    <t>经营性现金净流量除以营业总收入</t>
+  </si>
+  <si>
+    <t>dupontROE</t>
+  </si>
+  <si>
+    <t>净资产收益率, 算法: 归属母公司股东净利润/[(期初归属母公司股东的权益+期末归属母公司股东的权益)/2]*100%</t>
+  </si>
+  <si>
+    <t>dupontAssetStoEquity</t>
+  </si>
+  <si>
+    <t>权益乘数，反映企业财务杠杆效应强弱和财务风险, 算法: 平均总资产/平均归属于母公司的股东权益</t>
+  </si>
+  <si>
+    <t>dupontAssetTurn</t>
+  </si>
+  <si>
+    <t>总资产周转率，反映企业资产管理效率的指标, 算法: 营业总收入/[(期初资产总额+期末资产总额)/2]</t>
+  </si>
+  <si>
+    <t>dupontPnitoni</t>
+  </si>
+  <si>
+    <t>归属母公司股东的净利润/净利润，反映母公司控股子公司百分比</t>
+  </si>
+  <si>
+    <t>dupontNitogr</t>
+  </si>
+  <si>
+    <t>净利润/营业总收入，反映企业销售获利率</t>
+  </si>
+  <si>
+    <t>dupontTaxBurden</t>
+  </si>
+  <si>
+    <t>净利润/利润总额，反映企业税负水平，该比值高则税负较低</t>
+  </si>
+  <si>
+    <t>dupontIntburden</t>
+  </si>
+  <si>
+    <t>利润总额/息税前利润，反映企业利息负担</t>
+  </si>
+  <si>
+    <t>dupontEbittogr</t>
+  </si>
+  <si>
+    <t>息税前利润/营业总收入，反映企业经营利润率</t>
+  </si>
+  <si>
+    <t>performanceExpPubDate</t>
+  </si>
+  <si>
+    <t>业绩快报披露日</t>
+  </si>
+  <si>
+    <t>performanceExpStatDate</t>
+  </si>
+  <si>
+    <t>业绩快报统计日期</t>
+  </si>
+  <si>
+    <t>performanceExpUpdateDate</t>
+  </si>
+  <si>
+    <t>业绩快报披露日(最新)</t>
+  </si>
+  <si>
+    <t>performanceExpressTotalAsset</t>
+  </si>
+  <si>
+    <t>业绩快报总资产</t>
+  </si>
+  <si>
+    <t>performanceExpressNetAsset</t>
+  </si>
+  <si>
+    <t>业绩快报净资产</t>
+  </si>
+  <si>
+    <t>performanceExpressEPSChgPct</t>
+  </si>
+  <si>
+    <t>业绩每股收益增长率</t>
+  </si>
+  <si>
+    <t>performanceExpressROEWa</t>
+  </si>
+  <si>
+    <t>业绩快报净资产收益率ROE-加权</t>
+  </si>
+  <si>
+    <t>performanceExpressEPSDiluted</t>
+  </si>
+  <si>
+    <t>业绩快报每股收益EPS-摊薄</t>
+  </si>
+  <si>
+    <t>performanceExpressGRYOY</t>
+  </si>
+  <si>
+    <t>业绩快报营业总收入同比</t>
+  </si>
+  <si>
+    <t>performanceExpressOPYOY</t>
+  </si>
+  <si>
+    <t>业绩快报营业利润同比</t>
+  </si>
+  <si>
+    <t>profitForcastExpPubDate</t>
+  </si>
+  <si>
+    <t>业绩预告发布日期</t>
+  </si>
+  <si>
+    <t>profitForcastExpStatDate</t>
+  </si>
+  <si>
+    <t>业绩预告统计日期</t>
+  </si>
+  <si>
+    <t>profitForcastType</t>
+  </si>
+  <si>
+    <t>业绩预告类型</t>
+  </si>
+  <si>
+    <t>profitForcastAbstract</t>
+  </si>
+  <si>
+    <t>业绩预告摘要</t>
+  </si>
+  <si>
+    <t>profitForcastChgPctUp</t>
+  </si>
+  <si>
+    <t>预告归属于母公司的净利润增长上限(%)</t>
+  </si>
+  <si>
+    <t>profitForcastChgPctDwn</t>
+  </si>
+  <si>
+    <t>预告归属于母公司的净利润增长下限(%)</t>
+  </si>
+  <si>
+    <t>ipoDate</t>
+  </si>
+  <si>
+    <t>上市日期</t>
+  </si>
+  <si>
+    <t>outDate</t>
+  </si>
+  <si>
+    <t>退市日期</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>证券类型，其中1：股票，2：指数，3：其它，4：可转债，5：ETF</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>上市状态，其中1：上市，0：退市</t>
+  </si>
+  <si>
+    <t>发布日期</t>
+  </si>
+  <si>
+    <t>demandDepositRate</t>
+  </si>
+  <si>
+    <t>活期存款(不定期)</t>
+  </si>
+  <si>
+    <t>fixedDepositRate3Month</t>
+  </si>
+  <si>
+    <t>定期存款(三个月)</t>
+  </si>
+  <si>
+    <t>fixedDepositRate6Month</t>
+  </si>
+  <si>
+    <t>定期存款(半年)</t>
+  </si>
+  <si>
+    <t>fixedDepositRate1Year</t>
+  </si>
+  <si>
+    <t>定期存款整存整取(一年)</t>
+  </si>
+  <si>
+    <t>fixedDepositRate2Year</t>
+  </si>
+  <si>
+    <t>定期存款整存整取(二年)</t>
+  </si>
+  <si>
+    <t>fixedDepositRate3Year</t>
+  </si>
+  <si>
+    <t>定期存款整存整取(三年)</t>
+  </si>
+  <si>
+    <t>fixedDepositRate5Year</t>
+  </si>
+  <si>
+    <t>定期存款整存整取(五年)</t>
+  </si>
+  <si>
+    <t>installmentFixedDepositRate1Year</t>
+  </si>
+  <si>
+    <t>零存整取、整存零取、存本取息定期存款(一年)</t>
+  </si>
+  <si>
+    <t>installmentFixedDepositRate3Year</t>
+  </si>
+  <si>
+    <t>零存整取、整存零取、存本取息定期存款(三年)</t>
+  </si>
+  <si>
+    <t>installmentFixedDepositRate5Year</t>
+  </si>
+  <si>
+    <t>零存整取、整存零取、存本取息定期存款(五年)</t>
+  </si>
+  <si>
+    <t>effectiveDate</t>
+  </si>
+  <si>
+    <t>生效日期</t>
+  </si>
+  <si>
+    <t>bigInstitutionsRatioPre</t>
+  </si>
+  <si>
+    <t>人民币存款准备金率：大型存款类金融机构 调整前</t>
+  </si>
+  <si>
+    <t>bigInstitutionsRatioAfter</t>
+  </si>
+  <si>
+    <t>人民币存款准备金率：大型存款类金融机构 调整后</t>
+  </si>
+  <si>
+    <t>mediumInstitutionsRatioPre</t>
+  </si>
+  <si>
+    <t>人民币存款准备金率：中小型存款类金融机构 调整前</t>
+  </si>
+  <si>
+    <t>mediumInstitutionsRatioAfter</t>
+  </si>
+  <si>
+    <t>人民币存款准备金率：中小型存款类金融机构 调整后</t>
+  </si>
+  <si>
+    <t>loanRate6Month</t>
+  </si>
+  <si>
+    <t>6个月贷款利率</t>
+  </si>
+  <si>
+    <t>loanRate6MonthTo1Year</t>
+  </si>
+  <si>
+    <t>6个月至1年贷款利率</t>
+  </si>
+  <si>
+    <t>loanRate1YearTo3Year</t>
+  </si>
+  <si>
+    <t>1年至3年贷款利率</t>
+  </si>
+  <si>
+    <t>loanRate3YearTo5Year</t>
+  </si>
+  <si>
+    <t>3年至5年贷款利率</t>
+  </si>
+  <si>
+    <t>loanRateAbove5Year</t>
+  </si>
+  <si>
+    <t>5年以上贷款利率</t>
+  </si>
+  <si>
+    <t>mortgateRateBelow5Year</t>
+  </si>
+  <si>
+    <t>5年以下住房公积金贷款利率</t>
+  </si>
+  <si>
+    <t>mortgateRateAbove5Year</t>
+  </si>
+  <si>
+    <t>5年以上住房公积金贷款利率</t>
+  </si>
+  <si>
+    <t>statYear</t>
+  </si>
+  <si>
+    <t>统计年度</t>
+  </si>
+  <si>
+    <t>statMonth</t>
+  </si>
+  <si>
+    <t>统计月份</t>
+  </si>
+  <si>
+    <t>m0Month</t>
+  </si>
+  <si>
+    <t>货币供应量M0（月）</t>
+  </si>
+  <si>
+    <t>m0YOY</t>
+  </si>
+  <si>
+    <t>货币供应量M0（同比）</t>
+  </si>
+  <si>
+    <t>m0ChainRelative</t>
+  </si>
+  <si>
+    <t>货币供应量M0（环比）</t>
+  </si>
+  <si>
+    <t>m1Month</t>
+  </si>
+  <si>
+    <t>货币供应量M1（月）</t>
+  </si>
+  <si>
+    <t>m1YOY</t>
+  </si>
+  <si>
+    <t>货币供应量M1（同比）</t>
+  </si>
+  <si>
+    <t>m1ChainRelative</t>
+  </si>
+  <si>
+    <t>货币供应量M1（环比）</t>
+  </si>
+  <si>
+    <t>m2Month</t>
+  </si>
+  <si>
+    <t>货币供应量M2（月）</t>
+  </si>
+  <si>
+    <t>m2YOY</t>
+  </si>
+  <si>
+    <t>货币供应量M2（同比）</t>
+  </si>
+  <si>
+    <t>m2ChainRelative</t>
+  </si>
+  <si>
+    <t>货币供应量M2（环比）</t>
+  </si>
+  <si>
+    <t>m0Year</t>
+  </si>
+  <si>
+    <t>年货币供应量M0（亿元）</t>
+  </si>
+  <si>
+    <t>m0YearYOY</t>
+  </si>
+  <si>
+    <t>年货币供应量M0（同比）</t>
+  </si>
+  <si>
+    <t>m1Year</t>
+  </si>
+  <si>
+    <t>年货币供应量M1（亿元）</t>
+  </si>
+  <si>
+    <t>m1YearYOY</t>
+  </si>
+  <si>
+    <t>年货币供应量M1（同比）</t>
+  </si>
+  <si>
+    <t>m2Year</t>
+  </si>
+  <si>
+    <t>年货币供应量M2（亿元）</t>
+  </si>
+  <si>
+    <t>m2YearYOY</t>
+  </si>
+  <si>
+    <t>年货币供应量M2（同比）</t>
+  </si>
+  <si>
+    <t>成交量（累计，单位：股）</t>
+  </si>
+  <si>
+    <t>复权状态（1：后复权，2：前复权，3：不复权）</t>
+  </si>
+  <si>
+    <t>交易状态（1：正常交易，0：停牌）</t>
+  </si>
+  <si>
+    <t>是否ST股，1：是，0：否</t>
+  </si>
+  <si>
+    <t>foreAdjustFactor</t>
+  </si>
+  <si>
+    <t>向前复权因子，算法: 除权除息日前一个交易日的收盘价/除权除息日最近的一个交易日的前收盘价</t>
+  </si>
+  <si>
+    <t>backAdjustFactor</t>
+  </si>
+  <si>
+    <t>向后复权因子，算法: 除权除息日最近的一个交易日的前收盘价/除权除息日前一个交易日的收盘价</t>
+  </si>
+  <si>
+    <t>adjustFactor</t>
+  </si>
+  <si>
+    <t>本次复权因子</t>
+  </si>
+  <si>
+    <t>tradeStatus</t>
+  </si>
+  <si>
+    <t>交易状态，其中1：正常交易，0：停牌</t>
+  </si>
+  <si>
     <t>ArgName</t>
   </si>
   <si>
@@ -309,6 +1310,105 @@
   </si>
   <si>
     <t>2026-01-18</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>统计年份</t>
+  </si>
+  <si>
+    <t>quarter</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>{"arg_type": "SingleOption","option_range":[1,2,3,4]}</t>
+  </si>
+  <si>
+    <t>统计季度(1-4)</t>
+  </si>
+  <si>
+    <t>年份</t>
+  </si>
+  <si>
+    <t>yearType</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
+    <t>{"arg_type": "SingleOption","option_range":["report","operate"]}</t>
+  </si>
+  <si>
+    <t>年份类别: report=预案公告年份, operate=除权除息年份</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
+    <t>开始日期</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>结束日期</t>
+  </si>
+  <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>{"arg_type": "SingleOption","option_range":["0","1"]}</t>
+  </si>
+  <si>
+    <t>年份类别：0查询公告日期，1查询生效日期</t>
+  </si>
+  <si>
+    <t>2010-01</t>
+  </si>
+  <si>
+    <t>开始日期(YYYY-MM)</t>
+  </si>
+  <si>
+    <t>2024-12</t>
+  </si>
+  <si>
+    <t>结束日期(YYYY-MM)</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>开始年份(YYYY)</t>
+  </si>
+  <si>
+    <t>结束年份(YYYY)</t>
+  </si>
+  <si>
+    <t>2024-06-28</t>
+  </si>
+  <si>
+    <t>获取日期</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>查询日期</t>
   </si>
 </sst>
 </file>
@@ -321,7 +1421,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,9 +1430,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -341,6 +1440,13 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -676,12 +1782,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -785,31 +1906,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -818,122 +1936,126 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
@@ -987,7 +2109,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -997,7 +2119,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1071,7 +2193,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1106,7 +2227,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1283,38 +2403,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="28.25" customWidth="1"/>
-    <col min="3" max="3" width="13.75" customWidth="1"/>
-    <col min="4" max="4" width="39" customWidth="1"/>
-    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="56" customWidth="1"/>
+    <col min="1" max="1" width="21.375" customWidth="1"/>
+    <col min="2" max="2" width="37.125" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="54.5" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="7" max="7" width="71.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1331,10 +2451,10 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1351,23 +2471,534 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F2" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="http://baostock.com/mainContent?file=stockKData.md" tooltip="http://baostock.com/mainContent?file=stockKData.md"/>
-    <hyperlink ref="G3" r:id="rId2" display="http://baostock.com/mainContent?file=stockIndustry.md"/>
+    <hyperlink ref="G15" r:id="rId1" display="https://baostock.com/mainContent?file=reserveRatio.md"/>
+    <hyperlink ref="G16" r:id="rId2" display="https://baostock.com/mainContent?file=loanRate.md"/>
+    <hyperlink ref="G17" r:id="rId3" display="https://baostock.com/mainContent?file=supplyData.md"/>
+    <hyperlink ref="G18" r:id="rId4" display="https://baostock.com/mainContent?file=supplyDataYear.md"/>
+    <hyperlink ref="G19" r:id="rId5" display="https://baostock.com/mainContent?file=DailyUpdates.md"/>
+    <hyperlink ref="G20" r:id="rId5" display="https://baostock.com/mainContent?file=DailyUpdates.md"/>
+    <hyperlink ref="G21" r:id="rId5" display="https://baostock.com/mainContent?file=DailyUpdates.md"/>
+    <hyperlink ref="G23" r:id="rId6" display="https://baostock.com/mainContent?file=sz50Stock.md"/>
+    <hyperlink ref="G24" r:id="rId7" display="https://baostock.com/mainContent?file=hs300Stock.md"/>
+    <hyperlink ref="G25" r:id="rId8" display="https://baostock.com/mainContent?file=zz500Stock.md"/>
+    <hyperlink ref="G22" r:id="rId9" display="https://baostock.com/mainContent?file=StockBasicInfoAPI.md"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1375,34 +3006,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.8333333333333" customWidth="1"/>
-    <col min="2" max="2" width="29.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-    <col min="4" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="45.625" customWidth="1"/>
+    <col min="1" max="1" width="21.375" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="6" max="6" width="113.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
+      <c r="B1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1411,16 +3042,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1428,16 +3059,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1445,16 +3076,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1462,16 +3093,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1479,16 +3110,16 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1496,16 +3127,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1513,16 +3144,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1530,16 +3161,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1547,16 +3178,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1564,16 +3195,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1581,16 +3212,16 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1598,16 +3229,16 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1615,16 +3246,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1632,16 +3263,16 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1649,16 +3280,16 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1666,16 +3297,16 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1683,16 +3314,16 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1700,16 +3331,16 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1717,16 +3348,16 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1734,16 +3365,16 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1751,16 +3382,16 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1768,16 +3399,16 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1785,24 +3416,3284 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>176</v>
+      </c>
+      <c r="C33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>180</v>
+      </c>
+      <c r="C35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
+        <v>117</v>
+      </c>
+      <c r="F36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="s">
+        <v>121</v>
+      </c>
+      <c r="F40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F41" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" t="s">
+        <v>198</v>
+      </c>
+      <c r="C45" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" t="s">
+        <v>121</v>
+      </c>
+      <c r="F46" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" t="s">
+        <v>202</v>
+      </c>
+      <c r="C47" t="s">
+        <v>120</v>
+      </c>
+      <c r="D47" t="s">
+        <v>121</v>
+      </c>
+      <c r="F47" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" t="s">
+        <v>121</v>
+      </c>
+      <c r="F48" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D49" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
         <v>26</v>
       </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="B50" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" t="s">
+        <v>117</v>
+      </c>
+      <c r="F50" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" t="s">
+        <v>113</v>
+      </c>
+      <c r="F52" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" t="s">
+        <v>121</v>
+      </c>
+      <c r="F53" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" t="s">
+        <v>210</v>
+      </c>
+      <c r="C54" t="s">
+        <v>120</v>
+      </c>
+      <c r="D54" t="s">
+        <v>121</v>
+      </c>
+      <c r="F54" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" t="s">
+        <v>120</v>
+      </c>
+      <c r="D55" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C56" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" t="s">
+        <v>121</v>
+      </c>
+      <c r="F56" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" t="s">
+        <v>216</v>
+      </c>
+      <c r="C57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D57" t="s">
+        <v>121</v>
+      </c>
+      <c r="F57" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" t="s">
+        <v>218</v>
+      </c>
+      <c r="C58" t="s">
+        <v>120</v>
+      </c>
+      <c r="D58" t="s">
+        <v>121</v>
+      </c>
+      <c r="F58" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
+        <v>121</v>
+      </c>
+      <c r="F60" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="F61" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" t="s">
+        <v>222</v>
+      </c>
+      <c r="C62" t="s">
+        <v>120</v>
+      </c>
+      <c r="D62" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
+        <v>224</v>
+      </c>
+      <c r="C63" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" t="s">
+        <v>121</v>
+      </c>
+      <c r="F63" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" t="s">
+        <v>120</v>
+      </c>
+      <c r="D64" t="s">
+        <v>121</v>
+      </c>
+      <c r="F64" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65" t="s">
+        <v>121</v>
+      </c>
+      <c r="F65" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B66" t="s">
+        <v>230</v>
+      </c>
+      <c r="C66" t="s">
+        <v>120</v>
+      </c>
+      <c r="D66" t="s">
+        <v>121</v>
+      </c>
+      <c r="F66" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>34</v>
+      </c>
+      <c r="B67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" t="s">
+        <v>116</v>
+      </c>
+      <c r="D67" t="s">
+        <v>117</v>
+      </c>
+      <c r="F67" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>34</v>
+      </c>
+      <c r="B68" t="s">
+        <v>162</v>
+      </c>
+      <c r="C68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" t="s">
+        <v>121</v>
+      </c>
+      <c r="F68" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>34</v>
+      </c>
+      <c r="B69" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" t="s">
+        <v>113</v>
+      </c>
+      <c r="F69" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>34</v>
+      </c>
+      <c r="B70" t="s">
+        <v>233</v>
+      </c>
+      <c r="C70" t="s">
+        <v>120</v>
+      </c>
+      <c r="D70" t="s">
+        <v>121</v>
+      </c>
+      <c r="F70" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" t="s">
+        <v>235</v>
+      </c>
+      <c r="C71" t="s">
+        <v>120</v>
+      </c>
+      <c r="D71" t="s">
+        <v>121</v>
+      </c>
+      <c r="F71" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72" t="s">
+        <v>237</v>
+      </c>
+      <c r="C72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" t="s">
+        <v>121</v>
+      </c>
+      <c r="F72" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>34</v>
+      </c>
+      <c r="B73" t="s">
+        <v>239</v>
+      </c>
+      <c r="C73" t="s">
+        <v>120</v>
+      </c>
+      <c r="D73" t="s">
+        <v>121</v>
+      </c>
+      <c r="F73" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B74" t="s">
+        <v>241</v>
+      </c>
+      <c r="C74" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" t="s">
+        <v>121</v>
+      </c>
+      <c r="F74" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>34</v>
+      </c>
+      <c r="B75" t="s">
+        <v>243</v>
+      </c>
+      <c r="C75" t="s">
+        <v>120</v>
+      </c>
+      <c r="D75" t="s">
+        <v>121</v>
+      </c>
+      <c r="F75" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76" t="s">
+        <v>116</v>
+      </c>
+      <c r="D76" t="s">
+        <v>117</v>
+      </c>
+      <c r="F76" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" t="s">
+        <v>162</v>
+      </c>
+      <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
+        <v>121</v>
+      </c>
+      <c r="F77" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="F78" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" t="s">
+        <v>245</v>
+      </c>
+      <c r="C79" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" t="s">
+        <v>121</v>
+      </c>
+      <c r="F79" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>38</v>
+      </c>
+      <c r="B80" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" t="s">
+        <v>121</v>
+      </c>
+      <c r="F80" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>38</v>
+      </c>
+      <c r="B81" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" t="s">
+        <v>120</v>
+      </c>
+      <c r="D81" t="s">
+        <v>121</v>
+      </c>
+      <c r="F81" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" t="s">
+        <v>120</v>
+      </c>
+      <c r="D82" t="s">
+        <v>121</v>
+      </c>
+      <c r="F82" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>38</v>
+      </c>
+      <c r="B83" t="s">
+        <v>253</v>
+      </c>
+      <c r="C83" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" t="s">
+        <v>121</v>
+      </c>
+      <c r="F83" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" t="s">
+        <v>255</v>
+      </c>
+      <c r="C84" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" t="s">
+        <v>121</v>
+      </c>
+      <c r="F84" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>38</v>
+      </c>
+      <c r="B85" t="s">
+        <v>257</v>
+      </c>
+      <c r="C85" t="s">
+        <v>120</v>
+      </c>
+      <c r="D85" t="s">
+        <v>121</v>
+      </c>
+      <c r="F85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>42</v>
+      </c>
+      <c r="B86" t="s">
+        <v>115</v>
+      </c>
+      <c r="C86" t="s">
+        <v>116</v>
+      </c>
+      <c r="D86" t="s">
+        <v>117</v>
+      </c>
+      <c r="F86" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>42</v>
+      </c>
+      <c r="B87" t="s">
+        <v>162</v>
+      </c>
+      <c r="C87" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" t="s">
+        <v>121</v>
+      </c>
+      <c r="F87" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B88" t="s">
+        <v>164</v>
+      </c>
+      <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
+        <v>113</v>
+      </c>
+      <c r="F88" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>42</v>
+      </c>
+      <c r="B89" t="s">
+        <v>259</v>
+      </c>
+      <c r="C89" t="s">
+        <v>120</v>
+      </c>
+      <c r="D89" t="s">
+        <v>121</v>
+      </c>
+      <c r="F89" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" t="s">
+        <v>261</v>
+      </c>
+      <c r="C90" t="s">
+        <v>120</v>
+      </c>
+      <c r="D90" t="s">
+        <v>121</v>
+      </c>
+      <c r="F90" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>42</v>
+      </c>
+      <c r="B91" t="s">
+        <v>263</v>
+      </c>
+      <c r="C91" t="s">
+        <v>120</v>
+      </c>
+      <c r="D91" t="s">
+        <v>121</v>
+      </c>
+      <c r="F91" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>42</v>
+      </c>
+      <c r="B92" t="s">
+        <v>265</v>
+      </c>
+      <c r="C92" t="s">
+        <v>120</v>
+      </c>
+      <c r="D92" t="s">
+        <v>121</v>
+      </c>
+      <c r="F92" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>42</v>
+      </c>
+      <c r="B93" t="s">
+        <v>267</v>
+      </c>
+      <c r="C93" t="s">
+        <v>120</v>
+      </c>
+      <c r="D93" t="s">
+        <v>121</v>
+      </c>
+      <c r="F93" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>42</v>
+      </c>
+      <c r="B94" t="s">
+        <v>269</v>
+      </c>
+      <c r="C94" t="s">
+        <v>120</v>
+      </c>
+      <c r="D94" t="s">
+        <v>121</v>
+      </c>
+      <c r="F94" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" t="s">
+        <v>271</v>
+      </c>
+      <c r="C95" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95" t="s">
+        <v>121</v>
+      </c>
+      <c r="F95" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>42</v>
+      </c>
+      <c r="B96" t="s">
+        <v>273</v>
+      </c>
+      <c r="C96" t="s">
+        <v>120</v>
+      </c>
+      <c r="D96" t="s">
+        <v>121</v>
+      </c>
+      <c r="F96" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>46</v>
+      </c>
+      <c r="B97" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" t="s">
+        <v>116</v>
+      </c>
+      <c r="D97" t="s">
+        <v>117</v>
+      </c>
+      <c r="F97" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>46</v>
+      </c>
+      <c r="B98" t="s">
+        <v>275</v>
+      </c>
+      <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="F98" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>46</v>
+      </c>
+      <c r="B99" t="s">
+        <v>277</v>
+      </c>
+      <c r="C99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
+        <v>121</v>
+      </c>
+      <c r="F99" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>46</v>
+      </c>
+      <c r="B100" t="s">
+        <v>279</v>
+      </c>
+      <c r="C100" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" t="s">
+        <v>121</v>
+      </c>
+      <c r="F100" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>46</v>
+      </c>
+      <c r="B101" t="s">
+        <v>281</v>
+      </c>
+      <c r="C101" t="s">
+        <v>120</v>
+      </c>
+      <c r="D101" t="s">
+        <v>121</v>
+      </c>
+      <c r="F101" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>46</v>
+      </c>
+      <c r="B102" t="s">
+        <v>283</v>
+      </c>
+      <c r="C102" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" t="s">
+        <v>121</v>
+      </c>
+      <c r="F102" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>46</v>
+      </c>
+      <c r="B103" t="s">
+        <v>285</v>
+      </c>
+      <c r="C103" t="s">
+        <v>120</v>
+      </c>
+      <c r="D103" t="s">
+        <v>121</v>
+      </c>
+      <c r="F103" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>46</v>
+      </c>
+      <c r="B104" t="s">
+        <v>287</v>
+      </c>
+      <c r="C104" t="s">
+        <v>120</v>
+      </c>
+      <c r="D104" t="s">
+        <v>121</v>
+      </c>
+      <c r="F104" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>46</v>
+      </c>
+      <c r="B105" t="s">
+        <v>289</v>
+      </c>
+      <c r="C105" t="s">
+        <v>120</v>
+      </c>
+      <c r="D105" t="s">
+        <v>121</v>
+      </c>
+      <c r="F105" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>46</v>
+      </c>
+      <c r="B106" t="s">
+        <v>291</v>
+      </c>
+      <c r="C106" t="s">
+        <v>120</v>
+      </c>
+      <c r="D106" t="s">
+        <v>121</v>
+      </c>
+      <c r="F106" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" t="s">
+        <v>293</v>
+      </c>
+      <c r="C107" t="s">
+        <v>120</v>
+      </c>
+      <c r="D107" t="s">
+        <v>121</v>
+      </c>
+      <c r="F107" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>50</v>
+      </c>
+      <c r="B108" t="s">
+        <v>115</v>
+      </c>
+      <c r="C108" t="s">
+        <v>116</v>
+      </c>
+      <c r="D108" t="s">
+        <v>117</v>
+      </c>
+      <c r="F108" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" t="s">
+        <v>295</v>
+      </c>
+      <c r="C109" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" t="s">
+        <v>113</v>
+      </c>
+      <c r="F109" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>50</v>
+      </c>
+      <c r="B110" t="s">
+        <v>297</v>
+      </c>
+      <c r="C110" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110" t="s">
+        <v>121</v>
+      </c>
+      <c r="F110" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>50</v>
+      </c>
+      <c r="B111" t="s">
+        <v>299</v>
+      </c>
+      <c r="C111" t="s">
+        <v>116</v>
+      </c>
+      <c r="D111" t="s">
+        <v>121</v>
+      </c>
+      <c r="F111" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>50</v>
+      </c>
+      <c r="B112" t="s">
+        <v>301</v>
+      </c>
+      <c r="C112" t="s">
+        <v>116</v>
+      </c>
+      <c r="D112" t="s">
+        <v>121</v>
+      </c>
+      <c r="F112" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>50</v>
+      </c>
+      <c r="B113" t="s">
+        <v>303</v>
+      </c>
+      <c r="C113" t="s">
+        <v>120</v>
+      </c>
+      <c r="D113" t="s">
+        <v>121</v>
+      </c>
+      <c r="F113" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>50</v>
+      </c>
+      <c r="B114" t="s">
+        <v>305</v>
+      </c>
+      <c r="C114" t="s">
+        <v>120</v>
+      </c>
+      <c r="D114" t="s">
+        <v>121</v>
+      </c>
+      <c r="F114" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" t="s">
+        <v>115</v>
+      </c>
+      <c r="C115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D115" t="s">
+        <v>117</v>
+      </c>
+      <c r="F115" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>54</v>
+      </c>
+      <c r="B116" t="s">
+        <v>155</v>
+      </c>
+      <c r="C116" t="s">
+        <v>116</v>
+      </c>
+      <c r="D116" t="s">
+        <v>121</v>
+      </c>
+      <c r="F116" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>54</v>
+      </c>
+      <c r="B117" t="s">
+        <v>307</v>
+      </c>
+      <c r="C117" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117" t="s">
+        <v>121</v>
+      </c>
+      <c r="F117" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>54</v>
+      </c>
+      <c r="B118" t="s">
+        <v>309</v>
+      </c>
+      <c r="C118" t="s">
+        <v>112</v>
+      </c>
+      <c r="D118" t="s">
+        <v>121</v>
+      </c>
+      <c r="F118" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>54</v>
+      </c>
+      <c r="B119" t="s">
+        <v>311</v>
+      </c>
+      <c r="C119" t="s">
+        <v>116</v>
+      </c>
+      <c r="D119" t="s">
+        <v>121</v>
+      </c>
+      <c r="F119" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>54</v>
+      </c>
+      <c r="B120" t="s">
+        <v>313</v>
+      </c>
+      <c r="C120" t="s">
+        <v>116</v>
+      </c>
+      <c r="D120" t="s">
+        <v>121</v>
+      </c>
+      <c r="F120" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>58</v>
+      </c>
+      <c r="B121" t="s">
+        <v>162</v>
+      </c>
+      <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" t="s">
+        <v>113</v>
+      </c>
+      <c r="F121" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>58</v>
+      </c>
+      <c r="B122" t="s">
+        <v>316</v>
+      </c>
+      <c r="C122" t="s">
+        <v>120</v>
+      </c>
+      <c r="D122" t="s">
+        <v>121</v>
+      </c>
+      <c r="F122" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>58</v>
+      </c>
+      <c r="B123" t="s">
+        <v>318</v>
+      </c>
+      <c r="C123" t="s">
+        <v>120</v>
+      </c>
+      <c r="D123" t="s">
+        <v>121</v>
+      </c>
+      <c r="F123" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>58</v>
+      </c>
+      <c r="B124" t="s">
+        <v>320</v>
+      </c>
+      <c r="C124" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" t="s">
+        <v>121</v>
+      </c>
+      <c r="F124" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>58</v>
+      </c>
+      <c r="B125" t="s">
+        <v>322</v>
+      </c>
+      <c r="C125" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" t="s">
+        <v>121</v>
+      </c>
+      <c r="F125" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>58</v>
+      </c>
+      <c r="B126" t="s">
+        <v>324</v>
+      </c>
+      <c r="C126" t="s">
+        <v>120</v>
+      </c>
+      <c r="D126" t="s">
+        <v>121</v>
+      </c>
+      <c r="F126" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>58</v>
+      </c>
+      <c r="B127" t="s">
+        <v>326</v>
+      </c>
+      <c r="C127" t="s">
+        <v>120</v>
+      </c>
+      <c r="D127" t="s">
+        <v>121</v>
+      </c>
+      <c r="F127" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>58</v>
+      </c>
+      <c r="B128" t="s">
+        <v>328</v>
+      </c>
+      <c r="C128" t="s">
+        <v>120</v>
+      </c>
+      <c r="D128" t="s">
+        <v>121</v>
+      </c>
+      <c r="F128" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>58</v>
+      </c>
+      <c r="B129" t="s">
+        <v>330</v>
+      </c>
+      <c r="C129" t="s">
+        <v>120</v>
+      </c>
+      <c r="D129" t="s">
+        <v>121</v>
+      </c>
+      <c r="F129" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>58</v>
+      </c>
+      <c r="B130" t="s">
+        <v>332</v>
+      </c>
+      <c r="C130" t="s">
+        <v>120</v>
+      </c>
+      <c r="D130" t="s">
+        <v>121</v>
+      </c>
+      <c r="F130" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>58</v>
+      </c>
+      <c r="B131" t="s">
+        <v>334</v>
+      </c>
+      <c r="C131" t="s">
+        <v>120</v>
+      </c>
+      <c r="D131" t="s">
+        <v>121</v>
+      </c>
+      <c r="F131" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>64</v>
+      </c>
+      <c r="B132" t="s">
+        <v>162</v>
+      </c>
+      <c r="C132" t="s">
+        <v>112</v>
+      </c>
+      <c r="D132" t="s">
+        <v>113</v>
+      </c>
+      <c r="F132" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>64</v>
+      </c>
+      <c r="B133" t="s">
+        <v>336</v>
+      </c>
+      <c r="C133" t="s">
+        <v>112</v>
+      </c>
+      <c r="D133" t="s">
+        <v>121</v>
+      </c>
+      <c r="F133" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>64</v>
+      </c>
+      <c r="B134" t="s">
+        <v>338</v>
+      </c>
+      <c r="C134" t="s">
+        <v>120</v>
+      </c>
+      <c r="D134" t="s">
+        <v>121</v>
+      </c>
+      <c r="F134" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>64</v>
+      </c>
+      <c r="B135" t="s">
+        <v>340</v>
+      </c>
+      <c r="C135" t="s">
+        <v>120</v>
+      </c>
+      <c r="D135" t="s">
+        <v>121</v>
+      </c>
+      <c r="F135" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>64</v>
+      </c>
+      <c r="B136" t="s">
+        <v>342</v>
+      </c>
+      <c r="C136" t="s">
+        <v>120</v>
+      </c>
+      <c r="D136" t="s">
+        <v>121</v>
+      </c>
+      <c r="F136" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>64</v>
+      </c>
+      <c r="B137" t="s">
+        <v>344</v>
+      </c>
+      <c r="C137" t="s">
+        <v>120</v>
+      </c>
+      <c r="D137" t="s">
+        <v>121</v>
+      </c>
+      <c r="F137" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>67</v>
+      </c>
+      <c r="B138" t="s">
+        <v>162</v>
+      </c>
+      <c r="C138" t="s">
+        <v>112</v>
+      </c>
+      <c r="D138" t="s">
+        <v>113</v>
+      </c>
+      <c r="F138" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>67</v>
+      </c>
+      <c r="B139" t="s">
+        <v>346</v>
+      </c>
+      <c r="C139" t="s">
+        <v>120</v>
+      </c>
+      <c r="D139" t="s">
+        <v>121</v>
+      </c>
+      <c r="F139" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>67</v>
+      </c>
+      <c r="B140" t="s">
+        <v>348</v>
+      </c>
+      <c r="C140" t="s">
+        <v>120</v>
+      </c>
+      <c r="D140" t="s">
+        <v>121</v>
+      </c>
+      <c r="F140" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>67</v>
+      </c>
+      <c r="B141" t="s">
+        <v>350</v>
+      </c>
+      <c r="C141" t="s">
+        <v>120</v>
+      </c>
+      <c r="D141" t="s">
+        <v>121</v>
+      </c>
+      <c r="F141" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>67</v>
+      </c>
+      <c r="B142" t="s">
+        <v>352</v>
+      </c>
+      <c r="C142" t="s">
+        <v>120</v>
+      </c>
+      <c r="D142" t="s">
+        <v>121</v>
+      </c>
+      <c r="F142" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>67</v>
+      </c>
+      <c r="B143" t="s">
+        <v>354</v>
+      </c>
+      <c r="C143" t="s">
+        <v>120</v>
+      </c>
+      <c r="D143" t="s">
+        <v>121</v>
+      </c>
+      <c r="F143" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>67</v>
+      </c>
+      <c r="B144" t="s">
+        <v>356</v>
+      </c>
+      <c r="C144" t="s">
+        <v>120</v>
+      </c>
+      <c r="D144" t="s">
+        <v>121</v>
+      </c>
+      <c r="F144" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>67</v>
+      </c>
+      <c r="B145" t="s">
+        <v>358</v>
+      </c>
+      <c r="C145" t="s">
+        <v>120</v>
+      </c>
+      <c r="D145" t="s">
+        <v>121</v>
+      </c>
+      <c r="F145" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
         <v>70</v>
       </c>
+      <c r="B146" t="s">
+        <v>360</v>
+      </c>
+      <c r="C146" t="s">
+        <v>116</v>
+      </c>
+      <c r="D146" t="s">
+        <v>121</v>
+      </c>
+      <c r="F146" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>70</v>
+      </c>
+      <c r="B147" t="s">
+        <v>362</v>
+      </c>
+      <c r="C147" t="s">
+        <v>116</v>
+      </c>
+      <c r="D147" t="s">
+        <v>121</v>
+      </c>
+      <c r="F147" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>70</v>
+      </c>
+      <c r="B148" t="s">
+        <v>364</v>
+      </c>
+      <c r="C148" t="s">
+        <v>120</v>
+      </c>
+      <c r="D148" t="s">
+        <v>121</v>
+      </c>
+      <c r="F148" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>70</v>
+      </c>
+      <c r="B149" t="s">
+        <v>366</v>
+      </c>
+      <c r="C149" t="s">
+        <v>120</v>
+      </c>
+      <c r="D149" t="s">
+        <v>121</v>
+      </c>
+      <c r="F149" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>70</v>
+      </c>
+      <c r="B150" t="s">
+        <v>368</v>
+      </c>
+      <c r="C150" t="s">
+        <v>120</v>
+      </c>
+      <c r="D150" t="s">
+        <v>121</v>
+      </c>
+      <c r="F150" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>70</v>
+      </c>
+      <c r="B151" t="s">
+        <v>370</v>
+      </c>
+      <c r="C151" t="s">
+        <v>120</v>
+      </c>
+      <c r="D151" t="s">
+        <v>121</v>
+      </c>
+      <c r="F151" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>70</v>
+      </c>
+      <c r="B152" t="s">
+        <v>372</v>
+      </c>
+      <c r="C152" t="s">
+        <v>120</v>
+      </c>
+      <c r="D152" t="s">
+        <v>121</v>
+      </c>
+      <c r="F152" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>70</v>
+      </c>
+      <c r="B153" t="s">
+        <v>374</v>
+      </c>
+      <c r="C153" t="s">
+        <v>120</v>
+      </c>
+      <c r="D153" t="s">
+        <v>121</v>
+      </c>
+      <c r="F153" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>70</v>
+      </c>
+      <c r="B154" t="s">
+        <v>376</v>
+      </c>
+      <c r="C154" t="s">
+        <v>120</v>
+      </c>
+      <c r="D154" t="s">
+        <v>121</v>
+      </c>
+      <c r="F154" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>70</v>
+      </c>
+      <c r="B155" t="s">
+        <v>378</v>
+      </c>
+      <c r="C155" t="s">
+        <v>120</v>
+      </c>
+      <c r="D155" t="s">
+        <v>121</v>
+      </c>
+      <c r="F155" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>70</v>
+      </c>
+      <c r="B156" t="s">
+        <v>380</v>
+      </c>
+      <c r="C156" t="s">
+        <v>120</v>
+      </c>
+      <c r="D156" t="s">
+        <v>121</v>
+      </c>
+      <c r="F156" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>75</v>
+      </c>
+      <c r="B157" t="s">
+        <v>360</v>
+      </c>
+      <c r="C157" t="s">
+        <v>116</v>
+      </c>
+      <c r="D157" t="s">
+        <v>121</v>
+      </c>
+      <c r="F157" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>75</v>
+      </c>
+      <c r="B158" t="s">
+        <v>382</v>
+      </c>
+      <c r="C158" t="s">
+        <v>120</v>
+      </c>
+      <c r="D158" t="s">
+        <v>121</v>
+      </c>
+      <c r="F158" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>75</v>
+      </c>
+      <c r="B159" t="s">
+        <v>384</v>
+      </c>
+      <c r="C159" t="s">
+        <v>120</v>
+      </c>
+      <c r="D159" t="s">
+        <v>121</v>
+      </c>
+      <c r="F159" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>75</v>
+      </c>
+      <c r="B160" t="s">
+        <v>386</v>
+      </c>
+      <c r="C160" t="s">
+        <v>120</v>
+      </c>
+      <c r="D160" t="s">
+        <v>121</v>
+      </c>
+      <c r="F160" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>75</v>
+      </c>
+      <c r="B161" t="s">
+        <v>388</v>
+      </c>
+      <c r="C161" t="s">
+        <v>120</v>
+      </c>
+      <c r="D161" t="s">
+        <v>121</v>
+      </c>
+      <c r="F161" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>75</v>
+      </c>
+      <c r="B162" t="s">
+        <v>390</v>
+      </c>
+      <c r="C162" t="s">
+        <v>120</v>
+      </c>
+      <c r="D162" t="s">
+        <v>121</v>
+      </c>
+      <c r="F162" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>75</v>
+      </c>
+      <c r="B163" t="s">
+        <v>392</v>
+      </c>
+      <c r="C163" t="s">
+        <v>120</v>
+      </c>
+      <c r="D163" t="s">
+        <v>121</v>
+      </c>
+      <c r="F163" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>79</v>
+      </c>
+      <c r="B164" t="s">
+        <v>111</v>
+      </c>
+      <c r="C164" t="s">
+        <v>112</v>
+      </c>
+      <c r="D164" t="s">
+        <v>113</v>
+      </c>
+      <c r="F164" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>79</v>
+      </c>
+      <c r="B165" t="s">
+        <v>115</v>
+      </c>
+      <c r="C165" t="s">
+        <v>116</v>
+      </c>
+      <c r="D165" t="s">
+        <v>117</v>
+      </c>
+      <c r="F165" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>79</v>
+      </c>
+      <c r="B166" t="s">
+        <v>119</v>
+      </c>
+      <c r="C166" t="s">
+        <v>120</v>
+      </c>
+      <c r="D166" t="s">
+        <v>121</v>
+      </c>
+      <c r="F166" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>79</v>
+      </c>
+      <c r="B167" t="s">
+        <v>123</v>
+      </c>
+      <c r="C167" t="s">
+        <v>120</v>
+      </c>
+      <c r="D167" t="s">
+        <v>121</v>
+      </c>
+      <c r="F167" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>79</v>
+      </c>
+      <c r="B168" t="s">
+        <v>125</v>
+      </c>
+      <c r="C168" t="s">
+        <v>120</v>
+      </c>
+      <c r="D168" t="s">
+        <v>121</v>
+      </c>
+      <c r="F168" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>79</v>
+      </c>
+      <c r="B169" t="s">
+        <v>127</v>
+      </c>
+      <c r="C169" t="s">
+        <v>120</v>
+      </c>
+      <c r="D169" t="s">
+        <v>121</v>
+      </c>
+      <c r="F169" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>79</v>
+      </c>
+      <c r="B170" t="s">
+        <v>129</v>
+      </c>
+      <c r="C170" t="s">
+        <v>120</v>
+      </c>
+      <c r="D170" t="s">
+        <v>121</v>
+      </c>
+      <c r="F170" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>79</v>
+      </c>
+      <c r="B171" t="s">
+        <v>131</v>
+      </c>
+      <c r="C171" t="s">
+        <v>120</v>
+      </c>
+      <c r="D171" t="s">
+        <v>121</v>
+      </c>
+      <c r="F171" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>79</v>
+      </c>
+      <c r="B172" t="s">
+        <v>133</v>
+      </c>
+      <c r="C172" t="s">
+        <v>120</v>
+      </c>
+      <c r="D172" t="s">
+        <v>121</v>
+      </c>
+      <c r="F172" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>79</v>
+      </c>
+      <c r="B173" t="s">
+        <v>135</v>
+      </c>
+      <c r="C173" t="s">
+        <v>120</v>
+      </c>
+      <c r="D173" t="s">
+        <v>121</v>
+      </c>
+      <c r="F173" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>79</v>
+      </c>
+      <c r="B174" t="s">
+        <v>137</v>
+      </c>
+      <c r="C174" t="s">
+        <v>120</v>
+      </c>
+      <c r="D174" t="s">
+        <v>121</v>
+      </c>
+      <c r="F174" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>79</v>
+      </c>
+      <c r="B175" t="s">
+        <v>139</v>
+      </c>
+      <c r="C175" t="s">
+        <v>120</v>
+      </c>
+      <c r="D175" t="s">
+        <v>121</v>
+      </c>
+      <c r="F175" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>79</v>
+      </c>
+      <c r="B176" t="s">
+        <v>141</v>
+      </c>
+      <c r="C176" t="s">
+        <v>120</v>
+      </c>
+      <c r="D176" t="s">
+        <v>121</v>
+      </c>
+      <c r="F176" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>79</v>
+      </c>
+      <c r="B177" t="s">
+        <v>143</v>
+      </c>
+      <c r="C177" t="s">
+        <v>120</v>
+      </c>
+      <c r="D177" t="s">
+        <v>121</v>
+      </c>
+      <c r="F177" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>79</v>
+      </c>
+      <c r="B178" t="s">
+        <v>145</v>
+      </c>
+      <c r="C178" t="s">
+        <v>120</v>
+      </c>
+      <c r="D178" t="s">
+        <v>121</v>
+      </c>
+      <c r="F178" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>79</v>
+      </c>
+      <c r="B179" t="s">
+        <v>147</v>
+      </c>
+      <c r="C179" t="s">
+        <v>120</v>
+      </c>
+      <c r="D179" t="s">
+        <v>121</v>
+      </c>
+      <c r="F179" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>79</v>
+      </c>
+      <c r="B180" t="s">
+        <v>149</v>
+      </c>
+      <c r="C180" t="s">
+        <v>120</v>
+      </c>
+      <c r="D180" t="s">
+        <v>121</v>
+      </c>
+      <c r="F180" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>79</v>
+      </c>
+      <c r="B181" t="s">
+        <v>151</v>
+      </c>
+      <c r="C181" t="s">
+        <v>120</v>
+      </c>
+      <c r="D181" t="s">
+        <v>121</v>
+      </c>
+      <c r="F181" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>83</v>
+      </c>
+      <c r="B182" t="s">
+        <v>111</v>
+      </c>
+      <c r="C182" t="s">
+        <v>112</v>
+      </c>
+      <c r="D182" t="s">
+        <v>113</v>
+      </c>
+      <c r="F182" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>83</v>
+      </c>
+      <c r="B183" t="s">
+        <v>115</v>
+      </c>
+      <c r="C183" t="s">
+        <v>116</v>
+      </c>
+      <c r="D183" t="s">
+        <v>117</v>
+      </c>
+      <c r="F183" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>83</v>
+      </c>
+      <c r="B184" t="s">
+        <v>119</v>
+      </c>
+      <c r="C184" t="s">
+        <v>120</v>
+      </c>
+      <c r="D184" t="s">
+        <v>121</v>
+      </c>
+      <c r="F184" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>83</v>
+      </c>
+      <c r="B185" t="s">
+        <v>123</v>
+      </c>
+      <c r="C185" t="s">
+        <v>120</v>
+      </c>
+      <c r="D185" t="s">
+        <v>121</v>
+      </c>
+      <c r="F185" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>83</v>
+      </c>
+      <c r="B186" t="s">
+        <v>125</v>
+      </c>
+      <c r="C186" t="s">
+        <v>120</v>
+      </c>
+      <c r="D186" t="s">
+        <v>121</v>
+      </c>
+      <c r="F186" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>83</v>
+      </c>
+      <c r="B187" t="s">
+        <v>127</v>
+      </c>
+      <c r="C187" t="s">
+        <v>120</v>
+      </c>
+      <c r="D187" t="s">
+        <v>121</v>
+      </c>
+      <c r="F187" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>83</v>
+      </c>
+      <c r="B188" t="s">
+        <v>129</v>
+      </c>
+      <c r="C188" t="s">
+        <v>120</v>
+      </c>
+      <c r="D188" t="s">
+        <v>121</v>
+      </c>
+      <c r="F188" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>83</v>
+      </c>
+      <c r="B189" t="s">
+        <v>131</v>
+      </c>
+      <c r="C189" t="s">
+        <v>120</v>
+      </c>
+      <c r="D189" t="s">
+        <v>121</v>
+      </c>
+      <c r="F189" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>83</v>
+      </c>
+      <c r="B190" t="s">
+        <v>133</v>
+      </c>
+      <c r="C190" t="s">
+        <v>120</v>
+      </c>
+      <c r="D190" t="s">
+        <v>121</v>
+      </c>
+      <c r="F190" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>83</v>
+      </c>
+      <c r="B191" t="s">
+        <v>135</v>
+      </c>
+      <c r="C191" t="s">
+        <v>120</v>
+      </c>
+      <c r="D191" t="s">
+        <v>121</v>
+      </c>
+      <c r="F191" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>83</v>
+      </c>
+      <c r="B192" t="s">
+        <v>137</v>
+      </c>
+      <c r="C192" t="s">
+        <v>120</v>
+      </c>
+      <c r="D192" t="s">
+        <v>121</v>
+      </c>
+      <c r="F192" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>83</v>
+      </c>
+      <c r="B193" t="s">
+        <v>139</v>
+      </c>
+      <c r="C193" t="s">
+        <v>120</v>
+      </c>
+      <c r="D193" t="s">
+        <v>121</v>
+      </c>
+      <c r="F193" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>83</v>
+      </c>
+      <c r="B194" t="s">
+        <v>141</v>
+      </c>
+      <c r="C194" t="s">
+        <v>120</v>
+      </c>
+      <c r="D194" t="s">
+        <v>121</v>
+      </c>
+      <c r="F194" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>83</v>
+      </c>
+      <c r="B195" t="s">
+        <v>143</v>
+      </c>
+      <c r="C195" t="s">
+        <v>120</v>
+      </c>
+      <c r="D195" t="s">
+        <v>121</v>
+      </c>
+      <c r="F195" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>83</v>
+      </c>
+      <c r="B196" t="s">
+        <v>145</v>
+      </c>
+      <c r="C196" t="s">
+        <v>120</v>
+      </c>
+      <c r="D196" t="s">
+        <v>121</v>
+      </c>
+      <c r="F196" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>83</v>
+      </c>
+      <c r="B197" t="s">
+        <v>147</v>
+      </c>
+      <c r="C197" t="s">
+        <v>120</v>
+      </c>
+      <c r="D197" t="s">
+        <v>121</v>
+      </c>
+      <c r="F197" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>83</v>
+      </c>
+      <c r="B198" t="s">
+        <v>149</v>
+      </c>
+      <c r="C198" t="s">
+        <v>120</v>
+      </c>
+      <c r="D198" t="s">
+        <v>121</v>
+      </c>
+      <c r="F198" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>83</v>
+      </c>
+      <c r="B199" t="s">
+        <v>151</v>
+      </c>
+      <c r="C199" t="s">
+        <v>120</v>
+      </c>
+      <c r="D199" t="s">
+        <v>121</v>
+      </c>
+      <c r="F199" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>87</v>
+      </c>
+      <c r="B200" t="s">
+        <v>115</v>
+      </c>
+      <c r="C200" t="s">
+        <v>116</v>
+      </c>
+      <c r="D200" t="s">
+        <v>117</v>
+      </c>
+      <c r="F200" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>87</v>
+      </c>
+      <c r="B201" t="s">
+        <v>192</v>
+      </c>
+      <c r="C201" t="s">
+        <v>112</v>
+      </c>
+      <c r="D201" t="s">
+        <v>113</v>
+      </c>
+      <c r="F201" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>87</v>
+      </c>
+      <c r="B202" t="s">
+        <v>398</v>
+      </c>
+      <c r="C202" t="s">
+        <v>120</v>
+      </c>
+      <c r="D202" t="s">
+        <v>121</v>
+      </c>
+      <c r="F202" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>87</v>
+      </c>
+      <c r="B203" t="s">
+        <v>400</v>
+      </c>
+      <c r="C203" t="s">
+        <v>120</v>
+      </c>
+      <c r="D203" t="s">
+        <v>121</v>
+      </c>
+      <c r="F203" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>87</v>
+      </c>
+      <c r="B204" t="s">
+        <v>402</v>
+      </c>
+      <c r="C204" t="s">
+        <v>120</v>
+      </c>
+      <c r="D204" t="s">
+        <v>121</v>
+      </c>
+      <c r="F204" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>90</v>
+      </c>
+      <c r="B205" t="s">
+        <v>115</v>
+      </c>
+      <c r="C205" t="s">
+        <v>116</v>
+      </c>
+      <c r="D205" t="s">
+        <v>117</v>
+      </c>
+      <c r="F205" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>90</v>
+      </c>
+      <c r="B206" t="s">
+        <v>404</v>
+      </c>
+      <c r="C206" t="s">
+        <v>116</v>
+      </c>
+      <c r="D206" t="s">
+        <v>121</v>
+      </c>
+      <c r="F206" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>90</v>
+      </c>
+      <c r="B207" t="s">
+        <v>155</v>
+      </c>
+      <c r="C207" t="s">
+        <v>116</v>
+      </c>
+      <c r="D207" t="s">
+        <v>121</v>
+      </c>
+      <c r="F207" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>94</v>
+      </c>
+      <c r="B208" t="s">
+        <v>153</v>
+      </c>
+      <c r="C208" t="s">
+        <v>112</v>
+      </c>
+      <c r="D208" t="s">
+        <v>113</v>
+      </c>
+      <c r="F208" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>94</v>
+      </c>
+      <c r="B209" t="s">
+        <v>115</v>
+      </c>
+      <c r="C209" t="s">
+        <v>116</v>
+      </c>
+      <c r="D209" t="s">
+        <v>117</v>
+      </c>
+      <c r="F209" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>94</v>
+      </c>
+      <c r="B210" t="s">
+        <v>155</v>
+      </c>
+      <c r="C210" t="s">
+        <v>116</v>
+      </c>
+      <c r="D210" t="s">
+        <v>121</v>
+      </c>
+      <c r="F210" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>99</v>
+      </c>
+      <c r="B211" t="s">
+        <v>153</v>
+      </c>
+      <c r="C211" t="s">
+        <v>112</v>
+      </c>
+      <c r="D211" t="s">
+        <v>113</v>
+      </c>
+      <c r="F211" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>99</v>
+      </c>
+      <c r="B212" t="s">
+        <v>115</v>
+      </c>
+      <c r="C212" t="s">
+        <v>116</v>
+      </c>
+      <c r="D212" t="s">
+        <v>117</v>
+      </c>
+      <c r="F212" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>99</v>
+      </c>
+      <c r="B213" t="s">
+        <v>155</v>
+      </c>
+      <c r="C213" t="s">
+        <v>116</v>
+      </c>
+      <c r="D213" t="s">
+        <v>121</v>
+      </c>
+      <c r="F213" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>103</v>
+      </c>
+      <c r="B214" t="s">
+        <v>153</v>
+      </c>
+      <c r="C214" t="s">
+        <v>112</v>
+      </c>
+      <c r="D214" t="s">
+        <v>113</v>
+      </c>
+      <c r="F214" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>103</v>
+      </c>
+      <c r="B215" t="s">
+        <v>115</v>
+      </c>
+      <c r="C215" t="s">
+        <v>116</v>
+      </c>
+      <c r="D215" t="s">
+        <v>117</v>
+      </c>
+      <c r="F215" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>103</v>
+      </c>
+      <c r="B216" t="s">
+        <v>155</v>
+      </c>
+      <c r="C216" t="s">
+        <v>116</v>
+      </c>
+      <c r="D216" t="s">
+        <v>121</v>
+      </c>
+      <c r="F216" t="s">
+        <v>156</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F19" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1810,181 +6701,1125 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="18.1666666666667" customWidth="1"/>
+    <col min="1" max="1" width="21.375" customWidth="1"/>
     <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="9.33333333333333" customWidth="1"/>
-    <col min="4" max="4" width="10.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="161.25" customWidth="1"/>
-    <col min="7" max="7" width="74.3333333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="6" max="6" width="84.875" customWidth="1"/>
+    <col min="7" max="7" width="54.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
+      <c r="B1" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>117</v>
+      </c>
+      <c r="E2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>411</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>412</v>
+      </c>
+      <c r="E3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>414</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>415</v>
+      </c>
+      <c r="E4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>418</v>
+      </c>
+      <c r="E5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>421</v>
+      </c>
+      <c r="E6" t="s">
+        <v>422</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>89</v>
+        <v>421</v>
+      </c>
+      <c r="E7" t="s">
+        <v>424</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>117</v>
+      </c>
+      <c r="E8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>409</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>91</v>
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" t="s">
+        <v>409</v>
+      </c>
+      <c r="D10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" t="s">
+        <v>410</v>
+      </c>
+      <c r="G10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" t="s">
+        <v>428</v>
+      </c>
+      <c r="D11" t="s">
+        <v>429</v>
+      </c>
+      <c r="E11" t="s">
+        <v>430</v>
+      </c>
+      <c r="G11" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>432</v>
+      </c>
+      <c r="C12" t="s">
+        <v>428</v>
+      </c>
+      <c r="D12" t="s">
+        <v>433</v>
+      </c>
+      <c r="E12" t="s">
+        <v>424</v>
+      </c>
+      <c r="F12" t="s">
+        <v>434</v>
+      </c>
+      <c r="G12" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" t="s">
+        <v>409</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>410</v>
+      </c>
+      <c r="G13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" t="s">
+        <v>428</v>
+      </c>
+      <c r="D14" t="s">
+        <v>429</v>
+      </c>
+      <c r="E14" t="s">
+        <v>430</v>
+      </c>
+      <c r="G14" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D15" t="s">
+        <v>421</v>
+      </c>
+      <c r="E15" t="s">
+        <v>438</v>
+      </c>
+      <c r="F15" t="s">
+        <v>439</v>
+      </c>
+      <c r="G15" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>409</v>
+      </c>
+      <c r="D16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" t="s">
+        <v>410</v>
+      </c>
+      <c r="G16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C17" t="s">
+        <v>428</v>
+      </c>
+      <c r="D17" t="s">
+        <v>429</v>
+      </c>
+      <c r="E17" t="s">
+        <v>430</v>
+      </c>
+      <c r="G17" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>432</v>
+      </c>
+      <c r="C18" t="s">
+        <v>428</v>
+      </c>
+      <c r="D18" t="s">
+        <v>433</v>
+      </c>
+      <c r="E18" t="s">
+        <v>424</v>
+      </c>
+      <c r="F18" t="s">
+        <v>434</v>
+      </c>
+      <c r="G18" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>410</v>
+      </c>
+      <c r="G19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>427</v>
+      </c>
+      <c r="C20" t="s">
+        <v>428</v>
+      </c>
+      <c r="D20" t="s">
+        <v>429</v>
+      </c>
+      <c r="E20" t="s">
+        <v>430</v>
+      </c>
+      <c r="G20" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>432</v>
+      </c>
+      <c r="C21" t="s">
+        <v>428</v>
+      </c>
+      <c r="D21" t="s">
+        <v>433</v>
+      </c>
+      <c r="E21" t="s">
+        <v>424</v>
+      </c>
+      <c r="F21" t="s">
+        <v>434</v>
+      </c>
+      <c r="G21" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>409</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>410</v>
+      </c>
+      <c r="G22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>427</v>
+      </c>
+      <c r="C23" t="s">
+        <v>428</v>
+      </c>
+      <c r="D23" t="s">
+        <v>429</v>
+      </c>
+      <c r="E23" t="s">
+        <v>430</v>
+      </c>
+      <c r="G23" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>432</v>
+      </c>
+      <c r="C24" t="s">
+        <v>428</v>
+      </c>
+      <c r="D24" t="s">
+        <v>433</v>
+      </c>
+      <c r="E24" t="s">
+        <v>424</v>
+      </c>
+      <c r="F24" t="s">
+        <v>434</v>
+      </c>
+      <c r="G24" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" t="s">
+        <v>409</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>410</v>
+      </c>
+      <c r="G25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>427</v>
+      </c>
+      <c r="C26" t="s">
+        <v>428</v>
+      </c>
+      <c r="D26" t="s">
+        <v>429</v>
+      </c>
+      <c r="E26" t="s">
+        <v>430</v>
+      </c>
+      <c r="G26" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>432</v>
+      </c>
+      <c r="C27" t="s">
+        <v>428</v>
+      </c>
+      <c r="D27" t="s">
+        <v>433</v>
+      </c>
+      <c r="E27" t="s">
+        <v>424</v>
+      </c>
+      <c r="F27" t="s">
+        <v>434</v>
+      </c>
+      <c r="G27" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" t="s">
+        <v>409</v>
+      </c>
+      <c r="D28" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" t="s">
+        <v>427</v>
+      </c>
+      <c r="C29" t="s">
+        <v>428</v>
+      </c>
+      <c r="D29" t="s">
+        <v>429</v>
+      </c>
+      <c r="E29" t="s">
+        <v>430</v>
+      </c>
+      <c r="G29" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" t="s">
+        <v>432</v>
+      </c>
+      <c r="C30" t="s">
+        <v>428</v>
+      </c>
+      <c r="D30" t="s">
+        <v>433</v>
+      </c>
+      <c r="E30" t="s">
+        <v>424</v>
+      </c>
+      <c r="F30" t="s">
+        <v>434</v>
+      </c>
+      <c r="G30" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" t="s">
+        <v>409</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" t="s">
+        <v>410</v>
+      </c>
+      <c r="G31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>414</v>
+      </c>
+      <c r="C32" t="s">
+        <v>409</v>
+      </c>
+      <c r="D32" t="s">
+        <v>415</v>
+      </c>
+      <c r="E32" t="s">
+        <v>441</v>
+      </c>
+      <c r="G32" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
+        <v>417</v>
+      </c>
+      <c r="C33" t="s">
+        <v>409</v>
+      </c>
+      <c r="D33" t="s">
+        <v>418</v>
+      </c>
+      <c r="E33" t="s">
+        <v>443</v>
+      </c>
+      <c r="G33" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" t="s">
+        <v>409</v>
+      </c>
+      <c r="D34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" t="s">
+        <v>410</v>
+      </c>
+      <c r="G34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" t="s">
+        <v>414</v>
+      </c>
+      <c r="C35" t="s">
+        <v>409</v>
+      </c>
+      <c r="D35" t="s">
+        <v>415</v>
+      </c>
+      <c r="E35" t="s">
+        <v>441</v>
+      </c>
+      <c r="G35" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>417</v>
+      </c>
+      <c r="C36" t="s">
+        <v>409</v>
+      </c>
+      <c r="D36" t="s">
+        <v>418</v>
+      </c>
+      <c r="E36" t="s">
+        <v>443</v>
+      </c>
+      <c r="G36" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>409</v>
+      </c>
+      <c r="D37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" t="s">
+        <v>410</v>
+      </c>
+      <c r="G37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>414</v>
+      </c>
+      <c r="C38" t="s">
+        <v>409</v>
+      </c>
+      <c r="D38" t="s">
+        <v>415</v>
+      </c>
+      <c r="E38" t="s">
+        <v>441</v>
+      </c>
+      <c r="G38" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s">
+        <v>417</v>
+      </c>
+      <c r="C39" t="s">
+        <v>409</v>
+      </c>
+      <c r="D39" t="s">
+        <v>418</v>
+      </c>
+      <c r="E39" t="s">
+        <v>443</v>
+      </c>
+      <c r="G39" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" t="s">
+        <v>414</v>
+      </c>
+      <c r="C40" t="s">
+        <v>409</v>
+      </c>
+      <c r="D40" t="s">
+        <v>415</v>
+      </c>
+      <c r="E40" t="s">
+        <v>445</v>
+      </c>
+      <c r="G40" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
+        <v>417</v>
+      </c>
+      <c r="C41" t="s">
+        <v>409</v>
+      </c>
+      <c r="D41" t="s">
+        <v>418</v>
+      </c>
+      <c r="E41" t="s">
+        <v>443</v>
+      </c>
+      <c r="G41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" t="s">
+        <v>437</v>
+      </c>
+      <c r="C42" t="s">
+        <v>409</v>
+      </c>
+      <c r="D42" t="s">
+        <v>421</v>
+      </c>
+      <c r="E42" t="s">
+        <v>446</v>
+      </c>
+      <c r="F42" t="s">
+        <v>447</v>
+      </c>
+      <c r="G42" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" t="s">
+        <v>414</v>
+      </c>
+      <c r="C43" t="s">
+        <v>409</v>
+      </c>
+      <c r="D43" t="s">
+        <v>415</v>
+      </c>
+      <c r="E43" t="s">
+        <v>445</v>
+      </c>
+      <c r="G43" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" t="s">
+        <v>417</v>
+      </c>
+      <c r="C44" t="s">
+        <v>409</v>
+      </c>
+      <c r="D44" t="s">
+        <v>418</v>
+      </c>
+      <c r="E44" t="s">
+        <v>443</v>
+      </c>
+      <c r="G44" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
+        <v>414</v>
+      </c>
+      <c r="C45" t="s">
+        <v>409</v>
+      </c>
+      <c r="D45" t="s">
+        <v>415</v>
+      </c>
+      <c r="E45" t="s">
+        <v>449</v>
+      </c>
+      <c r="G45" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" t="s">
+        <v>417</v>
+      </c>
+      <c r="C46" t="s">
+        <v>409</v>
+      </c>
+      <c r="D46" t="s">
+        <v>418</v>
+      </c>
+      <c r="E46" t="s">
+        <v>451</v>
+      </c>
+      <c r="G46" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" t="s">
+        <v>414</v>
+      </c>
+      <c r="C47" t="s">
+        <v>409</v>
+      </c>
+      <c r="D47" t="s">
+        <v>415</v>
+      </c>
+      <c r="E47" t="s">
+        <v>453</v>
+      </c>
+      <c r="G47" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" t="s">
+        <v>417</v>
+      </c>
+      <c r="C48" t="s">
+        <v>409</v>
+      </c>
+      <c r="D48" t="s">
+        <v>418</v>
+      </c>
+      <c r="E48" t="s">
+        <v>430</v>
+      </c>
+      <c r="G48" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" t="s">
+        <v>409</v>
+      </c>
+      <c r="D49" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" t="s">
+        <v>456</v>
+      </c>
+      <c r="G49" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" t="s">
+        <v>409</v>
+      </c>
+      <c r="D50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" t="s">
+        <v>456</v>
+      </c>
+      <c r="G50" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" t="s">
+        <v>409</v>
+      </c>
+      <c r="D51" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" t="s">
+        <v>456</v>
+      </c>
+      <c r="G51" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" t="s">
+        <v>458</v>
+      </c>
+      <c r="C52" t="s">
+        <v>409</v>
+      </c>
+      <c r="D52" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52" t="s">
+        <v>456</v>
+      </c>
+      <c r="G52" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" t="s">
+        <v>409</v>
+      </c>
+      <c r="D53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" t="s">
+        <v>456</v>
+      </c>
+      <c r="G53" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" t="s">
+        <v>409</v>
+      </c>
+      <c r="D54" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" t="s">
+        <v>456</v>
+      </c>
+      <c r="G54" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" t="s">
+        <v>409</v>
+      </c>
+      <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
+        <v>456</v>
+      </c>
+      <c r="G55" t="s">
+        <v>459</v>
       </c>
     </row>
   </sheetData>
